--- a/Data point Supporting files/Germany 2020/Indicators.xlsx
+++ b/Data point Supporting files/Germany 2020/Indicators.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Indicators by country" sheetId="1" state="visible" r:id="rId2"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="321">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -40,22 +40,25 @@
     <t xml:space="preserve">GI 2020</t>
   </si>
   <si>
+    <t xml:space="preserve">ETI 2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPI 2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human right abuse scaled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WDI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biodiversity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCC</t>
+  </si>
+  <si>
     <t xml:space="preserve">KOFGI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPI 2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human right abuse scaled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WDI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biodiversity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCC</t>
   </si>
   <si>
     <t xml:space="preserve">Afghanistan</t>
@@ -1139,8 +1142,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J1000"/>
-  <sheetFormatPr defaultColWidth="11.23828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:K1000"/>
+  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.44"/>
@@ -1150,7 +1153,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="9" style="0" width="10.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="12" style="0" width="10.67"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1184,10 +1189,13 @@
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="5" t="n">
         <v>51.258162</v>
@@ -1216,10 +1224,13 @@
       <c r="J2" s="3" t="n">
         <v>7.4</v>
       </c>
+      <c r="K2" s="6" t="n">
+        <v>4.1013</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>34.273602</v>
@@ -1248,10 +1259,13 @@
       <c r="J3" s="3" t="n">
         <v>3.6</v>
       </c>
+      <c r="K3" s="6" t="n">
+        <v>0.9008</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>40.343461</v>
@@ -1280,10 +1294,13 @@
       <c r="J4" s="3" t="n">
         <v>4.4</v>
       </c>
+      <c r="K4" s="6" t="n">
+        <v>4.1338</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>19.585812</v>
@@ -1312,10 +1329,13 @@
       <c r="J5" s="3" t="n">
         <v>3.1</v>
       </c>
+      <c r="K5" s="6" t="n">
+        <v>2.0654</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>12.473464</v>
@@ -1344,10 +1364,13 @@
       <c r="J6" s="3" t="n">
         <v>2</v>
       </c>
+      <c r="K6" s="6" t="n">
+        <v>1.2147</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>44.076545</v>
@@ -1376,10 +1399,13 @@
       <c r="J7" s="3" t="n">
         <v>7.3</v>
       </c>
+      <c r="K7" s="6" t="n">
+        <v>3.7806</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>22.649846</v>
@@ -1408,10 +1434,13 @@
       <c r="J8" s="3" t="n">
         <v>3.7</v>
       </c>
+      <c r="K8" s="6" t="n">
+        <v>1.4982</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>28.705658</v>
@@ -1440,10 +1469,13 @@
       <c r="J9" s="3" t="n">
         <v>3.9</v>
       </c>
+      <c r="K9" s="6" t="n">
+        <v>1.8514</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>31.402014</v>
@@ -1472,10 +1504,13 @@
       <c r="J10" s="3" t="n">
         <v>3.9</v>
       </c>
+      <c r="K10" s="6" t="n">
+        <v>3.6987</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>31.580599</v>
@@ -1504,10 +1539,13 @@
       <c r="J11" s="3" t="n">
         <v>2.7</v>
       </c>
+      <c r="K11" s="6" t="n">
+        <v>1.9185</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="5" t="n">
         <v>16.940461</v>
@@ -1536,10 +1574,13 @@
       <c r="J12" s="3" t="n">
         <v>2.9</v>
       </c>
+      <c r="K12" s="6" t="n">
+        <v>1.3636</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>16.61553</v>
@@ -1568,10 +1609,13 @@
       <c r="J13" s="3" t="n">
         <v>2.5</v>
       </c>
+      <c r="K13" s="6" t="n">
+        <v>1.4155</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>9.078647</v>
@@ -1600,10 +1644,13 @@
       <c r="J14" s="3" t="n">
         <v>2.8</v>
       </c>
+      <c r="K14" s="6" t="n">
+        <v>0.5559</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>36.326732</v>
@@ -1632,10 +1679,13 @@
       <c r="J15" s="3" t="n">
         <v>4.6</v>
       </c>
+      <c r="K15" s="6" t="n">
+        <v>2.1793</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" s="5" t="n">
         <v>28.709337</v>
@@ -1664,10 +1714,13 @@
       <c r="J16" s="3" t="n">
         <v>3.8</v>
       </c>
+      <c r="K16" s="6" t="n">
+        <v>1.5303</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>43.069097</v>
@@ -1696,10 +1749,13 @@
       <c r="J17" s="3" t="n">
         <v>4.7</v>
       </c>
+      <c r="K17" s="6" t="n">
+        <v>3.8994</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>21.751673</v>
@@ -1728,10 +1784,13 @@
       <c r="J18" s="3" t="n">
         <v>2.7</v>
       </c>
+      <c r="K18" s="6" t="n">
+        <v>3.5622</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19" s="5" t="n">
         <v>38.700013</v>
@@ -1760,10 +1819,13 @@
       <c r="J19" s="3" t="n">
         <v>3</v>
       </c>
+      <c r="K19" s="6" t="n">
+        <v>2.5613</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>13.104212</v>
@@ -1792,10 +1854,13 @@
       <c r="J20" s="3" t="n">
         <v>3.2</v>
       </c>
+      <c r="K20" s="6" t="n">
+        <v>0.6989</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B21" s="5" t="n">
         <v>36.364602</v>
@@ -1824,10 +1889,13 @@
       <c r="J21" s="3" t="n">
         <v>5.1</v>
       </c>
+      <c r="K21" s="6" t="n">
+        <v>4.0791</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>34.724178</v>
@@ -1856,10 +1924,13 @@
       <c r="J22" s="3" t="n">
         <v>7.4</v>
       </c>
+      <c r="K22" s="6" t="n">
+        <v>4.7837</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B23" s="5" t="n">
         <v>17.582276</v>
@@ -1888,10 +1959,13 @@
       <c r="J23" s="3" t="n">
         <v>2.4</v>
       </c>
+      <c r="K23" s="6" t="n">
+        <v>1.4982</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>23.214981</v>
@@ -1920,10 +1994,13 @@
       <c r="J24" s="3" t="n">
         <v>4.5</v>
       </c>
+      <c r="K24" s="6" t="n">
+        <v>2.6322</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>54.341502</v>
@@ -1952,10 +2029,13 @@
       <c r="J25" s="3" t="n">
         <v>5.3</v>
       </c>
+      <c r="K25" s="6" t="n">
+        <v>3.7892</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>37.860579</v>
@@ -1984,10 +2064,13 @@
       <c r="J26" s="3" t="n">
         <v>5</v>
       </c>
+      <c r="K26" s="6" t="n">
+        <v>1.3654</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>7.867588</v>
@@ -2016,10 +2099,13 @@
       <c r="J27" s="3" t="n">
         <v>5.3</v>
       </c>
+      <c r="K27" s="6" t="n">
+        <v>2.956</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B28" s="5" t="n">
         <v>32.417276</v>
@@ -2048,10 +2134,13 @@
       <c r="J28" s="3" t="n">
         <v>4.8</v>
       </c>
+      <c r="K28" s="6" t="n">
+        <v>2.6383</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>19.296292</v>
@@ -2080,10 +2169,13 @@
       <c r="J29" s="3" t="n">
         <v>2.7</v>
       </c>
+      <c r="K29" s="6" t="n">
+        <v>2.2436</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>31.777924</v>
@@ -2112,10 +2204,13 @@
       <c r="J30" s="3" t="n">
         <v>3.1</v>
       </c>
+      <c r="K30" s="6" t="n">
+        <v>0.7585</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>37.364382</v>
@@ -2144,10 +2239,13 @@
       <c r="J31" s="3" t="n">
         <v>7.1</v>
       </c>
+      <c r="K31" s="6" t="n">
+        <v>3.9785</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B32" s="5" t="n">
         <v>47.00734</v>
@@ -2176,10 +2274,13 @@
       <c r="J32" s="3" t="n">
         <v>6.3</v>
       </c>
+      <c r="K32" s="6" t="n">
+        <v>4.4386</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B33" s="5" t="n">
         <v>42.944415</v>
@@ -2208,10 +2309,13 @@
       <c r="J33" s="3" t="n">
         <v>5.7</v>
       </c>
+      <c r="K33" s="6" t="n">
+        <v>3.2339</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B34" s="5" t="n">
         <v>43.957272</v>
@@ -2240,10 +2344,13 @@
       <c r="J34" s="3" t="n">
         <v>6.9</v>
       </c>
+      <c r="K34" s="6" t="n">
+        <v>3.9915</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B35" s="5" t="n">
         <v>17.4789</v>
@@ -2272,10 +2379,13 @@
       <c r="J35" s="3" t="n">
         <v>2.4</v>
       </c>
+      <c r="K35" s="6" t="n">
+        <v>0.9084</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B36" s="5" t="n">
         <v>25.11032</v>
@@ -2304,10 +2414,13 @@
       <c r="J36" s="3" t="n">
         <v>4.1</v>
       </c>
+      <c r="K36" s="6" t="n">
+        <v>3.8311</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B37" s="5" t="n">
         <v>20.151807</v>
@@ -2336,10 +2449,13 @@
       <c r="J37" s="3" t="n">
         <v>3.5</v>
       </c>
+      <c r="K37" s="6" t="n">
+        <v>1.251</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B38" s="5" t="n">
         <v>50.324223</v>
@@ -2368,10 +2484,13 @@
       <c r="J38" s="3" t="n">
         <v>8.9</v>
       </c>
+      <c r="K38" s="6" t="n">
+        <v>4.8502</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B39" s="5" t="n">
         <v>48.348618</v>
@@ -2400,10 +2519,13 @@
       <c r="J39" s="3" t="n">
         <v>8.8</v>
       </c>
+      <c r="K39" s="6" t="n">
+        <v>5.2594</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B40" s="5" t="n">
         <v>16.009826</v>
@@ -2432,10 +2554,13 @@
       <c r="J40" s="3" t="n">
         <v>2.6</v>
       </c>
+      <c r="K40" s="6" t="n">
+        <v>1.4618</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B41" s="5" t="n">
         <v>31.107614</v>
@@ -2464,10 +2589,13 @@
       <c r="J41" s="3" t="n">
         <v>3.4</v>
       </c>
+      <c r="K41" s="6" t="n">
+        <v>2.5159</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B42" s="5" t="n">
         <v>34.242912</v>
@@ -2496,10 +2624,13 @@
       <c r="J42" s="3" t="n">
         <v>3.2</v>
       </c>
+      <c r="K42" s="6" t="n">
+        <v>2.9228</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B43" s="5" t="n">
         <v>47.851348</v>
@@ -2528,10 +2659,13 @@
       <c r="J43" s="3" t="n">
         <v>7.2</v>
       </c>
+      <c r="K43" s="6" t="n">
+        <v>3.4615</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B44" s="5" t="n">
         <v>24.166205</v>
@@ -2560,10 +2694,13 @@
       <c r="J44" s="3" t="n">
         <v>2.3</v>
       </c>
+      <c r="K44" s="6" t="n">
+        <v>1.941</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B45" s="5" t="n">
         <v>27.330719</v>
@@ -2592,10 +2729,13 @@
       <c r="J45" s="3" t="n">
         <v>3.2</v>
       </c>
+      <c r="K45" s="6" t="n">
+        <v>0.5725</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B46" s="5" t="n">
         <v>38.015098</v>
@@ -2624,10 +2764,13 @@
       <c r="J46" s="3" t="n">
         <v>3.7</v>
       </c>
+      <c r="K46" s="6" t="n">
+        <v>4.0089</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B47" s="5" t="n">
         <v>21.001929</v>
@@ -2656,10 +2799,13 @@
       <c r="J47" s="3" t="n">
         <v>2.4</v>
       </c>
+      <c r="K47" s="6" t="n">
+        <v>0.638</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B48" s="5" t="n">
         <v>18.301748</v>
@@ -2688,10 +2834,13 @@
       <c r="J48" s="3" t="n">
         <v>1.9</v>
       </c>
+      <c r="K48" s="6" t="n">
+        <v>0.6372</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B49" s="5" t="n">
         <v>45.431604</v>
@@ -2720,10 +2869,13 @@
       <c r="J49" s="3" t="n">
         <v>8.3</v>
       </c>
+      <c r="K49" s="6" t="n">
+        <v>4.349</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B50" s="5" t="n">
         <v>4.206832</v>
@@ -2752,10 +2904,13 @@
       <c r="J50" s="3" t="n">
         <v>0.9</v>
       </c>
+      <c r="K50" s="6" t="n">
+        <v>0.6726</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B51" s="5" t="n">
         <v>42.332353</v>
@@ -2784,10 +2939,13 @@
       <c r="J51" s="3" t="n">
         <v>6.4</v>
       </c>
+      <c r="K51" s="6" t="n">
+        <v>5.205</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B52" s="5" t="n">
         <v>28.725723</v>
@@ -2816,10 +2974,13 @@
       <c r="J52" s="3" t="n">
         <v>3.8</v>
       </c>
+      <c r="K52" s="6" t="n">
+        <v>2.3567</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B53" s="5" t="n">
         <v>32.71961</v>
@@ -2848,10 +3009,13 @@
       <c r="J53" s="3" t="n">
         <v>4.9</v>
       </c>
+      <c r="K53" s="6" t="n">
+        <v>2.6952</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B54" s="5" t="n">
         <v>44.198857</v>
@@ -2880,10 +3044,13 @@
       <c r="J54" s="3" t="n">
         <v>5</v>
       </c>
+      <c r="K54" s="6" t="n">
+        <v>3.9466</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B55" s="5" t="n">
         <v>39.324839</v>
@@ -2912,10 +3079,13 @@
       <c r="J55" s="3" t="n">
         <v>4.2</v>
       </c>
+      <c r="K55" s="6" t="n">
+        <v>3.2642</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B56" s="5" t="n">
         <v>35.928175</v>
@@ -2944,10 +3114,13 @@
       <c r="J56" s="3" t="n">
         <v>3.7</v>
       </c>
+      <c r="K56" s="6" t="n">
+        <v>2.3858</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B57" s="5" t="n">
         <v>49.705037</v>
@@ -2976,10 +3149,13 @@
       <c r="J57" s="3" t="n">
         <v>7.1</v>
       </c>
+      <c r="K57" s="6" t="n">
+        <v>4.3332</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B58" s="5" t="n">
         <v>52.126475</v>
@@ -3008,10 +3184,13 @@
       <c r="J58" s="3" t="n">
         <v>7.8</v>
       </c>
+      <c r="K58" s="6" t="n">
+        <v>4.8849</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B59" s="5" t="n">
         <v>11.82682</v>
@@ -3040,10 +3219,13 @@
       <c r="J59" s="3" t="n">
         <v>1.5</v>
       </c>
+      <c r="K59" s="6" t="n">
+        <v>0.5363</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B60" s="5" t="n">
         <v>39.650038</v>
@@ -3072,10 +3254,13 @@
       <c r="J60" s="3" t="n">
         <v>6.9</v>
       </c>
+      <c r="K60" s="6" t="n">
+        <v>4.1433</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B61" s="5" t="n">
         <v>27.273607</v>
@@ -3104,10 +3289,13 @@
       <c r="J61" s="3" t="n">
         <v>3.3</v>
       </c>
+      <c r="K61" s="6" t="n">
+        <v>3.3864</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B62" s="5" t="n">
         <v>0</v>
@@ -3136,10 +3324,13 @@
       <c r="J62" s="3" t="n">
         <v>1.8</v>
       </c>
+      <c r="K62" s="6" t="n">
+        <v>0.6234</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B63" s="5" t="n">
         <v>14.231227</v>
@@ -3168,10 +3359,13 @@
       <c r="J63" s="3" t="n">
         <v>2.1</v>
       </c>
+      <c r="K63" s="6" t="n">
+        <v>0.5208</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B64" s="5" t="n">
         <v>15.05161</v>
@@ -3200,10 +3394,13 @@
       <c r="J64" s="3" t="n">
         <v>2.3</v>
       </c>
+      <c r="K64" s="6" t="n">
+        <v>1.1556</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B65" s="5" t="n">
         <v>42.609409</v>
@@ -3232,10 +3429,13 @@
       <c r="J65" s="3" t="n">
         <v>6.1</v>
       </c>
+      <c r="K65" s="6" t="n">
+        <v>5.0296</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B66" s="5" t="n">
         <v>37.348983</v>
@@ -3264,10 +3464,13 @@
       <c r="J66" s="3" t="n">
         <v>6.3</v>
       </c>
+      <c r="K66" s="6" t="n">
+        <v>4.7512</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B67" s="5" t="n">
         <v>24.039541</v>
@@ -3296,10 +3499,13 @@
       <c r="J67" s="3" t="n">
         <v>2.4</v>
       </c>
+      <c r="K67" s="6" t="n">
+        <v>1.0456</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B68" s="5" t="n">
         <v>8.729124</v>
@@ -3328,10 +3534,13 @@
       <c r="J68" s="3" t="n">
         <v>1.8</v>
       </c>
+      <c r="K68" s="6" t="n">
+        <v>0.5717</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B69" s="5" t="n">
         <v>24.446981</v>
@@ -3360,10 +3569,13 @@
       <c r="J69" s="3" t="n">
         <v>5.1</v>
       </c>
+      <c r="K69" s="6" t="n">
+        <v>3.275</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B70" s="5" t="n">
         <v>25.385162</v>
@@ -3392,10 +3604,13 @@
       <c r="J70" s="3" t="n">
         <v>3</v>
       </c>
+      <c r="K70" s="6" t="n">
+        <v>0.7585</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B71" s="5" t="n">
         <v>31.80132</v>
@@ -3424,10 +3639,13 @@
       <c r="J71" s="3" t="n">
         <v>3.4</v>
       </c>
+      <c r="K71" s="6" t="n">
+        <v>0.736</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B72" s="5" t="n">
         <v>29.325128</v>
@@ -3456,10 +3674,13 @@
       <c r="J72" s="3" t="n">
         <v>3.6</v>
       </c>
+      <c r="K72" s="6" t="n">
+        <v>2.6897</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B73" s="5" t="n">
         <v>19.732506</v>
@@ -3488,10 +3709,13 @@
       <c r="J73" s="3" t="n">
         <v>3.1</v>
       </c>
+      <c r="K73" s="6" t="n">
+        <v>2.0654</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B74" s="5" t="n">
         <v>41.853454</v>
@@ -3520,10 +3744,13 @@
       <c r="J74" s="3" t="n">
         <v>4.9</v>
       </c>
+      <c r="K74" s="6" t="n">
+        <v>2.4888</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B75" s="5" t="n">
         <v>24.263611</v>
@@ -3552,10 +3779,13 @@
       <c r="J75" s="3" t="n">
         <v>7.4</v>
       </c>
+      <c r="K75" s="6" t="n">
+        <v>5.0068</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B76" s="5" t="n">
         <v>47.733897</v>
@@ -3584,10 +3814,13 @@
       <c r="J76" s="3" t="n">
         <v>7.8</v>
       </c>
+      <c r="K76" s="6" t="n">
+        <v>4.265</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B77" s="5" t="n">
         <v>30.228446</v>
@@ -3616,10 +3849,13 @@
       <c r="J77" s="3" t="n">
         <v>5</v>
       </c>
+      <c r="K77" s="6" t="n">
+        <v>4.6499</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B78" s="5" t="n">
         <v>50.619189</v>
@@ -3648,10 +3884,13 @@
       <c r="J78" s="3" t="n">
         <v>7.2</v>
       </c>
+      <c r="K78" s="6" t="n">
+        <v>2.9114</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B79" s="5" t="n">
         <v>41.862496</v>
@@ -3680,10 +3919,13 @@
       <c r="J79" s="3" t="n">
         <v>5.8</v>
       </c>
+      <c r="K79" s="6" t="n">
+        <v>2.8161</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B80" s="5" t="n">
         <v>10.48863</v>
@@ -3712,10 +3954,13 @@
       <c r="J80" s="3" t="n">
         <v>1.7</v>
       </c>
+      <c r="K80" s="6" t="n">
+        <v>1.5342</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B81" s="5" t="n">
         <v>25.888181</v>
@@ -3744,10 +3989,13 @@
       <c r="J81" s="3" t="n">
         <v>2.9</v>
       </c>
+      <c r="K81" s="6" t="n">
+        <v>0.6413</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B82" s="5" t="n">
         <v>9.657037</v>
@@ -3776,10 +4024,13 @@
       <c r="J82" s="3" t="n">
         <v>1.9</v>
       </c>
+      <c r="K82" s="6" t="n">
+        <v>0.6189</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B83" s="5" t="n">
         <v>31.770835</v>
@@ -3808,10 +4059,13 @@
       <c r="J83" s="3" t="n">
         <v>4.6</v>
       </c>
+      <c r="K83" s="6" t="n">
+        <v>2.8441</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B84" s="5" t="n">
         <v>44.528455</v>
@@ -3840,10 +4094,13 @@
       <c r="J84" s="3" t="n">
         <v>4.2</v>
       </c>
+      <c r="K84" s="6" t="n">
+        <v>2.2516</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B85" s="5" t="n">
         <v>45.186069</v>
@@ -3872,10 +4129,13 @@
       <c r="J85" s="3" t="n">
         <v>5.6</v>
       </c>
+      <c r="K85" s="6" t="n">
+        <v>3.8436</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B86" s="5" t="n">
         <v>48.870321</v>
@@ -3904,10 +4164,13 @@
       <c r="J86" s="3" t="n">
         <v>5.1</v>
       </c>
+      <c r="K86" s="6" t="n">
+        <v>3.3986</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B87" s="5" t="n">
         <v>0.353967</v>
@@ -3936,10 +4199,13 @@
       <c r="J87" s="3" t="n">
         <v>3.2</v>
       </c>
+      <c r="K87" s="6" t="n">
+        <v>1.339</v>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B88" s="5" t="n">
         <v>18.419937</v>
@@ -3968,10 +4234,13 @@
       <c r="J88" s="3" t="n">
         <v>2.2</v>
       </c>
+      <c r="K88" s="6" t="n">
+        <v>0.862</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B89" s="5" t="n">
         <v>24.32736</v>
@@ -4000,10 +4269,13 @@
       <c r="J89" s="3" t="n">
         <v>3.6</v>
       </c>
+      <c r="K89" s="6" t="n">
+        <v>0.5538</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B90" s="5" t="n">
         <v>37.55407</v>
@@ -4032,10 +4304,13 @@
       <c r="J90" s="3" t="n">
         <v>6.6</v>
       </c>
+      <c r="K90" s="6" t="n">
+        <v>3.9493</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B91" s="5" t="n">
         <v>30.263009</v>
@@ -4064,10 +4339,13 @@
       <c r="J91" s="3" t="n">
         <v>3.6</v>
       </c>
+      <c r="K91" s="6" t="n">
+        <v>3.4875</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B92" s="5" t="n">
         <v>11.117981</v>
@@ -4096,10 +4374,13 @@
       <c r="J92" s="3" t="n">
         <v>1</v>
       </c>
+      <c r="K92" s="6" t="n">
+        <v>1.2372</v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B93" s="5" t="n">
         <v>29.423936</v>
@@ -4128,10 +4409,13 @@
       <c r="J93" s="3" t="n">
         <v>3.5</v>
       </c>
+      <c r="K93" s="6" t="n">
+        <v>1.9747</v>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B94" s="5" t="n">
         <v>33.221373</v>
@@ -4160,10 +4444,13 @@
       <c r="J94" s="3" t="n">
         <v>3.4</v>
       </c>
+      <c r="K94" s="6" t="n">
+        <v>2.8109</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B95" s="5" t="n">
         <v>38.382585</v>
@@ -4192,10 +4479,13 @@
       <c r="J95" s="3" t="n">
         <v>5.6</v>
       </c>
+      <c r="K95" s="6" t="n">
+        <v>4.1279</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B96" s="5" t="n">
         <v>28.936539</v>
@@ -4224,10 +4514,13 @@
       <c r="J96" s="3" t="n">
         <v>4.4</v>
       </c>
+      <c r="K96" s="6" t="n">
+        <v>3.1991</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B97" s="5" t="n">
         <v>36.073166</v>
@@ -4256,10 +4549,13 @@
       <c r="J97" s="3" t="n">
         <v>5.8</v>
       </c>
+      <c r="K97" s="6" t="n">
+        <v>3.0083</v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B98" s="5" t="n">
         <v>31.204435</v>
@@ -4288,10 +4584,13 @@
       <c r="J98" s="3" t="n">
         <v>4.1</v>
       </c>
+      <c r="K98" s="6" t="n">
+        <v>1.774</v>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B99" s="5" t="n">
         <v>40.633649</v>
@@ -4320,10 +4619,13 @@
       <c r="J99" s="3" t="n">
         <v>4.2</v>
       </c>
+      <c r="K99" s="6" t="n">
+        <v>2.4877</v>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B100" s="5" t="n">
         <v>42.704137</v>
@@ -4352,10 +4654,13 @@
       <c r="J100" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="K100" s="6" t="n">
+        <v>2.1583</v>
+      </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B101" s="5" t="n">
         <v>19.861322</v>
@@ -4384,10 +4689,13 @@
       <c r="J101" s="3" t="n">
         <v>2.6</v>
       </c>
+      <c r="K101" s="6" t="n">
+        <v>0.6547</v>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B102" s="5" t="n">
         <v>43.810341</v>
@@ -4416,10 +4724,13 @@
       <c r="J102" s="3" t="n">
         <v>5.4</v>
       </c>
+      <c r="K102" s="6" t="n">
+        <v>2.2329</v>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B103" s="5" t="n">
         <v>37.176598</v>
@@ -4448,10 +4759,13 @@
       <c r="J103" s="3" t="n">
         <v>6.3</v>
       </c>
+      <c r="K103" s="6" t="n">
+        <v>2.5036</v>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B104" s="5" t="n">
         <v>44.778237</v>
@@ -4480,10 +4794,13 @@
       <c r="J104" s="3" t="n">
         <v>7.3</v>
       </c>
+      <c r="K104" s="6" t="n">
+        <v>5.0927</v>
+      </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B105" s="5" t="n">
         <v>53.566974</v>
@@ -4512,10 +4829,13 @@
       <c r="J105" s="3" t="n">
         <v>6.6</v>
       </c>
+      <c r="K105" s="6" t="n">
+        <v>4.9238</v>
+      </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B106" s="5" t="n">
         <v>8.102204</v>
@@ -4544,10 +4864,13 @@
       <c r="J106" s="3" t="n">
         <v>1</v>
       </c>
+      <c r="K106" s="6" t="n">
+        <v>0.5593</v>
+      </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B107" s="5" t="n">
         <v>18.49054</v>
@@ -4576,10 +4899,13 @@
       <c r="J107" s="3" t="n">
         <v>2.5</v>
       </c>
+      <c r="K107" s="6" t="n">
+        <v>0.671</v>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B108" s="5" t="n">
         <v>5.618063</v>
@@ -4608,10 +4934,13 @@
       <c r="J108" s="3" t="n">
         <v>1.2</v>
       </c>
+      <c r="K108" s="6" t="n">
+        <v>0.4358</v>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B109" s="5" t="n">
         <v>18.151903</v>
@@ -4640,10 +4969,13 @@
       <c r="J109" s="3" t="n">
         <v>3.3</v>
       </c>
+      <c r="K109" s="6" t="n">
+        <v>0.8247</v>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B110" s="5" t="n">
         <v>42.721725</v>
@@ -4672,10 +5004,13 @@
       <c r="J110" s="3" t="n">
         <v>7.7</v>
       </c>
+      <c r="K110" s="6" t="n">
+        <v>3.055</v>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B111" s="5" t="n">
         <v>38.573531</v>
@@ -4704,10 +5039,13 @@
       <c r="J111" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="K111" s="6" t="n">
+        <v>3.1893</v>
+      </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B112" s="5" t="n">
         <v>23.76274</v>
@@ -4736,10 +5074,13 @@
       <c r="J112" s="3" t="n">
         <v>3.9</v>
       </c>
+      <c r="K112" s="6" t="n">
+        <v>1.394</v>
+      </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B113" s="5" t="n">
         <v>34.317542</v>
@@ -4768,10 +5109,13 @@
       <c r="J113" s="3" t="n">
         <v>3.7</v>
       </c>
+      <c r="K113" s="6" t="n">
+        <v>2.9598</v>
+      </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B114" s="5" t="n">
         <v>20.891512</v>
@@ -4800,10 +5144,13 @@
       <c r="J114" s="3" t="n">
         <v>7.1</v>
       </c>
+      <c r="K114" s="6" t="n">
+        <v>4.0452</v>
+      </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B115" s="5" t="n">
         <v>18.997025</v>
@@ -4832,10 +5179,13 @@
       <c r="J115" s="3" t="n">
         <v>2.4</v>
       </c>
+      <c r="K115" s="6" t="n">
+        <v>0.7719</v>
+      </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B116" s="5" t="n">
         <v>32.394035</v>
@@ -4864,10 +5214,13 @@
       <c r="J116" s="3" t="n">
         <v>3.9</v>
       </c>
+      <c r="K116" s="6" t="n">
+        <v>3.61</v>
+      </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B117" s="5" t="n">
         <v>21.549619</v>
@@ -4896,10 +5249,13 @@
       <c r="J117" s="3" t="n">
         <v>3.3</v>
       </c>
+      <c r="K117" s="6" t="n">
+        <v>1.7818</v>
+      </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B118" s="5" t="n">
         <v>37.035247</v>
@@ -4928,10 +5284,13 @@
       <c r="J118" s="3" t="n">
         <v>6.7</v>
       </c>
+      <c r="K118" s="6" t="n">
+        <v>4.335</v>
+      </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B119" s="5" t="n">
         <v>20.961062</v>
@@ -4960,10 +5319,13 @@
       <c r="J119" s="3" t="n">
         <v>2.4</v>
       </c>
+      <c r="K119" s="6" t="n">
+        <v>0.6414</v>
+      </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B120" s="5" t="n">
         <v>34.661847</v>
@@ -4992,10 +5354,13 @@
       <c r="J120" s="3" t="n">
         <v>3.5</v>
       </c>
+      <c r="K120" s="6" t="n">
+        <v>1.5632</v>
+      </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B121" s="5" t="n">
         <v>30.06481</v>
@@ -5024,10 +5389,13 @@
       <c r="J121" s="3" t="n">
         <v>4.7</v>
       </c>
+      <c r="K121" s="6" t="n">
+        <v>3.561</v>
+      </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B122" s="5" t="n">
         <v>36.300569</v>
@@ -5056,10 +5424,13 @@
       <c r="J122" s="3" t="n">
         <v>4.6</v>
       </c>
+      <c r="K122" s="6" t="n">
+        <v>1.5547</v>
+      </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B123" s="5" t="n">
         <v>35.339818</v>
@@ -5088,10 +5459,13 @@
       <c r="J123" s="3" t="n">
         <v>3.9</v>
       </c>
+      <c r="K123" s="6" t="n">
+        <v>3.3595</v>
+      </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B124" s="5" t="n">
         <v>29.890382</v>
@@ -5120,10 +5494,13 @@
       <c r="J124" s="3" t="n">
         <v>2.9</v>
       </c>
+      <c r="K124" s="6" t="n">
+        <v>0.833</v>
+      </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B125" s="5" t="n">
         <v>33.612156</v>
@@ -5152,10 +5529,13 @@
       <c r="J125" s="3" t="n">
         <v>4.1</v>
       </c>
+      <c r="K125" s="6" t="n">
+        <v>1.9781</v>
+      </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B126" s="5" t="n">
         <v>35.962737</v>
@@ -5184,10 +5564,13 @@
       <c r="J126" s="3" t="n">
         <v>6.9</v>
       </c>
+      <c r="K126" s="6" t="n">
+        <v>2.3856</v>
+      </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B127" s="5" t="n">
         <v>43.889875</v>
@@ -5216,10 +5599,13 @@
       <c r="J127" s="3" t="n">
         <v>5.6</v>
       </c>
+      <c r="K127" s="6" t="n">
+        <v>2.86</v>
+      </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B128" s="5" t="n">
         <v>24.771291</v>
@@ -5248,10 +5634,13 @@
       <c r="J128" s="3" t="n">
         <v>4.7</v>
       </c>
+      <c r="K128" s="6" t="n">
+        <v>3.1941</v>
+      </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B129" s="5" t="n">
         <v>30.381888</v>
@@ -5280,10 +5669,13 @@
       <c r="J129" s="3" t="n">
         <v>3.7</v>
       </c>
+      <c r="K129" s="6" t="n">
+        <v>2.9645</v>
+      </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B130" s="5" t="n">
         <v>40.354454</v>
@@ -5312,10 +5704,13 @@
       <c r="J130" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="K130" s="6" t="n">
+        <v>3.5572</v>
+      </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B131" s="5" t="n">
         <v>5.900481</v>
@@ -5344,10 +5739,13 @@
       <c r="J131" s="3" t="n">
         <v>1.8</v>
       </c>
+      <c r="K131" s="6" t="n">
+        <v>0.4691</v>
+      </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B132" s="5" t="n">
         <v>27.810632</v>
@@ -5376,10 +5774,13 @@
       <c r="J132" s="3" t="n">
         <v>2.1</v>
       </c>
+      <c r="K132" s="6" t="n">
+        <v>0.5208</v>
+      </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B133" s="5" t="n">
         <v>18.775015</v>
@@ -5408,10 +5809,13 @@
       <c r="J133" s="3" t="n">
         <v>1.5</v>
       </c>
+      <c r="K133" s="6" t="n">
+        <v>1.7266</v>
+      </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B134" s="5" t="n">
         <v>44.272317</v>
@@ -5440,10 +5844,13 @@
       <c r="J134" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="K134" s="6" t="n">
+        <v>2.4567</v>
+      </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B135" s="5" t="n">
         <v>39.341428</v>
@@ -5472,10 +5879,13 @@
       <c r="J135" s="3" t="n">
         <v>7.9</v>
       </c>
+      <c r="K135" s="6" t="n">
+        <v>4.6986</v>
+      </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B136" s="5" t="n">
         <v>43.866292</v>
@@ -5504,10 +5914,13 @@
       <c r="J136" s="3" t="n">
         <v>7.3</v>
       </c>
+      <c r="K136" s="6" t="n">
+        <v>4.9743</v>
+      </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B137" s="5" t="n">
         <v>52.496655</v>
@@ -5536,10 +5949,13 @@
       <c r="J137" s="3" t="n">
         <v>6.1</v>
       </c>
+      <c r="K137" s="6" t="n">
+        <v>4.8711</v>
+      </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B138" s="5" t="n">
         <v>32.633657</v>
@@ -5568,10 +5984,13 @@
       <c r="J138" s="3" t="n">
         <v>4.2</v>
       </c>
+      <c r="K138" s="6" t="n">
+        <v>1.845</v>
+      </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B139" s="5" t="n">
         <v>17.454318</v>
@@ -5600,10 +6019,13 @@
       <c r="J139" s="3" t="n">
         <v>1.5</v>
       </c>
+      <c r="K139" s="6" t="n">
+        <v>0.8046</v>
+      </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B140" s="5" t="n">
         <v>28.443163</v>
@@ -5632,10 +6054,13 @@
       <c r="J140" s="3" t="n">
         <v>3.6</v>
       </c>
+      <c r="K140" s="6" t="n">
+        <v>1.5783</v>
+      </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B141" s="5" t="n">
         <v>41.347153</v>
@@ -5664,10 +6089,13 @@
       <c r="J141" s="3" t="n">
         <v>5.6</v>
       </c>
+      <c r="K141" s="6" t="n">
+        <v>3.7384</v>
+      </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B142" s="5" t="n">
         <v>24.69584</v>
@@ -5696,10 +6124,13 @@
       <c r="J142" s="3" t="n">
         <v>3.3</v>
       </c>
+      <c r="K142" s="6" t="n">
+        <v>2.0612</v>
+      </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B143" s="5" t="n">
         <v>32.102574</v>
@@ -5728,10 +6159,13 @@
       <c r="J143" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="K143" s="6" t="n">
+        <v>2.2055</v>
+      </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B144" s="5" t="n">
         <v>45.718306</v>
@@ -5760,10 +6194,13 @@
       <c r="J144" s="3" t="n">
         <v>7</v>
       </c>
+      <c r="K144" s="6" t="n">
+        <v>1.8724</v>
+      </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B145" s="5" t="n">
         <v>37.718044</v>
@@ -5792,10 +6229,13 @@
       <c r="J145" s="3" t="n">
         <v>5.1</v>
       </c>
+      <c r="K145" s="6" t="n">
+        <v>2.6217</v>
+      </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B146" s="5" t="n">
         <v>23.912048</v>
@@ -5824,10 +6264,13 @@
       <c r="J146" s="3" t="n">
         <v>3.9</v>
       </c>
+      <c r="K146" s="6" t="n">
+        <v>1.211</v>
+      </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B147" s="5" t="n">
         <v>34.470227</v>
@@ -5856,10 +6299,13 @@
       <c r="J147" s="3" t="n">
         <v>4</v>
       </c>
+      <c r="K147" s="6" t="n">
+        <v>2.8278</v>
+      </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B148" s="5" t="n">
         <v>22.805407</v>
@@ -5888,10 +6334,13 @@
       <c r="J148" s="3" t="n">
         <v>2.2</v>
       </c>
+      <c r="K148" s="6" t="n">
+        <v>0.8244</v>
+      </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B149" s="5" t="n">
         <v>5.907227</v>
@@ -5920,10 +6369,13 @@
       <c r="J149" s="3" t="n">
         <v>1.8</v>
       </c>
+      <c r="K149" s="6" t="n">
+        <v>0.5384</v>
+      </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B150" s="5" t="n">
         <v>27.347676</v>
@@ -5952,10 +6404,13 @@
       <c r="J150" s="3" t="n">
         <v>5.1</v>
       </c>
+      <c r="K150" s="6" t="n">
+        <v>1.606</v>
+      </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B151" s="5" t="n">
         <v>20.847319</v>
@@ -5984,10 +6439,13 @@
       <c r="J151" s="3" t="n">
         <v>1.4</v>
       </c>
+      <c r="K151" s="6" t="n">
+        <v>1.3737</v>
+      </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B152" s="5" t="n">
         <v>48.088966</v>
@@ -6016,10 +6474,13 @@
       <c r="J152" s="3" t="n">
         <v>7.4</v>
       </c>
+      <c r="K152" s="6" t="n">
+        <v>4.4273</v>
+      </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B153" s="5" t="n">
         <v>21.549619</v>
@@ -6048,10 +6509,13 @@
       <c r="J153" s="3" t="n">
         <v>3.3</v>
       </c>
+      <c r="K153" s="6" t="n">
+        <v>1.7818</v>
+      </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B154" s="5" t="n">
         <v>29.732222</v>
@@ -6080,10 +6544,13 @@
       <c r="J154" s="3" t="n">
         <v>3.8</v>
       </c>
+      <c r="K154" s="6" t="n">
+        <v>0.6735</v>
+      </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B155" s="5" t="n">
         <v>25.235547</v>
@@ -6112,10 +6579,13 @@
       <c r="J155" s="3" t="n">
         <v>2.9</v>
       </c>
+      <c r="K155" s="6" t="n">
+        <v>2.2544</v>
+      </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B156" s="5" t="n">
         <v>28.409796</v>
@@ -6144,10 +6614,13 @@
       <c r="J156" s="3" t="n">
         <v>5.3</v>
       </c>
+      <c r="K156" s="6" t="n">
+        <v>3.5403</v>
+      </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B157" s="5" t="n">
         <v>24.01539</v>
@@ -6176,10 +6649,13 @@
       <c r="J157" s="3" t="n">
         <v>2.7</v>
       </c>
+      <c r="K157" s="6" t="n">
+        <v>1.9721</v>
+      </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B158" s="5" t="n">
         <v>26.724609</v>
@@ -6208,10 +6684,13 @@
       <c r="J158" s="3" t="n">
         <v>3.5</v>
       </c>
+      <c r="K158" s="6" t="n">
+        <v>2.2006</v>
+      </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B159" s="5" t="n">
         <v>25.060124</v>
@@ -6240,10 +6719,13 @@
       <c r="J159" s="3" t="n">
         <v>4.1</v>
       </c>
+      <c r="K159" s="6" t="n">
+        <v>2.3355</v>
+      </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B160" s="5" t="n">
         <v>23.326505</v>
@@ -6272,10 +6754,13 @@
       <c r="J160" s="3" t="n">
         <v>3.9</v>
       </c>
+      <c r="K160" s="6" t="n">
+        <v>2.6342</v>
+      </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B161" s="5" t="n">
         <v>36.479802</v>
@@ -6304,10 +6789,13 @@
       <c r="J161" s="3" t="n">
         <v>5.3</v>
       </c>
+      <c r="K161" s="6" t="n">
+        <v>3.5362</v>
+      </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B162" s="5" t="n">
         <v>29.860825</v>
@@ -6336,10 +6824,13 @@
       <c r="J162" s="3" t="n">
         <v>2.8</v>
       </c>
+      <c r="K162" s="6" t="n">
+        <v>1.5395</v>
+      </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B163" s="5" t="n">
         <v>32.148484</v>
@@ -6368,10 +6859,13 @@
       <c r="J163" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="K163" s="6" t="n">
+        <v>3.8914</v>
+      </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B164" s="5" t="n">
         <v>32.538898</v>
@@ -6400,10 +6894,13 @@
       <c r="J164" s="3" t="n">
         <v>4.4</v>
       </c>
+      <c r="K164" s="6" t="n">
+        <v>1.5255</v>
+      </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B165" s="5" t="n">
         <v>23.197602</v>
@@ -6432,10 +6929,13 @@
       <c r="J165" s="3" t="n">
         <v>2.6</v>
       </c>
+      <c r="K165" s="6" t="n">
+        <v>1.859</v>
+      </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B166" s="5" t="n">
         <v>41.123274</v>
@@ -6464,10 +6964,13 @@
       <c r="J166" s="3" t="n">
         <v>7.2</v>
       </c>
+      <c r="K166" s="6" t="n">
+        <v>4.5008</v>
+      </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B167" s="5" t="n">
         <v>5.129249</v>
@@ -6496,10 +6999,13 @@
       <c r="J167" s="3" t="n">
         <v>0.9</v>
       </c>
+      <c r="K167" s="6" t="n">
+        <v>0.5581</v>
+      </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B168" s="5" t="n">
         <v>23.835352</v>
@@ -6528,10 +7034,13 @@
       <c r="J168" s="3" t="n">
         <v>4.1</v>
       </c>
+      <c r="K168" s="6" t="n">
+        <v>0.8409</v>
+      </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B169" s="5" t="n">
         <v>18.399929</v>
@@ -6560,10 +7069,13 @@
       <c r="J169" s="3" t="n">
         <v>2.6</v>
       </c>
+      <c r="K169" s="6" t="n">
+        <v>0.7227</v>
+      </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B170" s="5" t="n">
         <v>36.857665</v>
@@ -6592,10 +7104,13 @@
       <c r="J170" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="K170" s="6" t="n">
+        <v>3.6326</v>
+      </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B171" s="5" t="n">
         <v>56.079599</v>
@@ -6624,10 +7139,13 @@
       <c r="J171" s="3" t="n">
         <v>7.3</v>
       </c>
+      <c r="K171" s="6" t="n">
+        <v>5.2064</v>
+      </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B172" s="5" t="n">
         <v>38.25525</v>
@@ -6656,10 +7174,13 @@
       <c r="J172" s="3" t="n">
         <v>4.8</v>
       </c>
+      <c r="K172" s="6" t="n">
+        <v>2.0415</v>
+      </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B173" s="5" t="n">
         <v>16.756514</v>
@@ -6688,10 +7209,13 @@
       <c r="J173" s="3" t="n">
         <v>1.5</v>
       </c>
+      <c r="K173" s="6" t="n">
+        <v>2.1753</v>
+      </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B174" s="5" t="n">
         <v>57.032176</v>
@@ -6720,10 +7244,13 @@
       <c r="J174" s="3" t="n">
         <v>9.2</v>
       </c>
+      <c r="K174" s="6" t="n">
+        <v>4.8791</v>
+      </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B175" s="5" t="n">
         <v>19.669363</v>
@@ -6752,10 +7279,13 @@
       <c r="J175" s="3" t="n">
         <v>2.2</v>
       </c>
+      <c r="K175" s="6" t="n">
+        <v>0.6397</v>
+      </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B176" s="5" t="n">
         <v>33.535081</v>
@@ -6784,10 +7314,13 @@
       <c r="J176" s="3" t="n">
         <v>4.9</v>
       </c>
+      <c r="K176" s="6" t="n">
+        <v>3.1961</v>
+      </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B177" s="5" t="n">
         <v>49.88207</v>
@@ -6816,10 +7349,13 @@
       <c r="J177" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="K177" s="6" t="n">
+        <v>4.3662</v>
+      </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B178" s="5" t="n">
         <v>35.61735</v>
@@ -6848,10 +7384,13 @@
       <c r="J178" s="3" t="n">
         <v>5.2</v>
       </c>
+      <c r="K178" s="6" t="n">
+        <v>3.5456</v>
+      </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B179" s="5" t="n">
         <v>38.197037</v>
@@ -6880,10 +7419,13 @@
       <c r="J179" s="3" t="n">
         <v>5</v>
       </c>
+      <c r="K179" s="6" t="n">
+        <v>3.7403</v>
+      </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B180" s="5" t="n">
         <v>10.644826</v>
@@ -6912,10 +7454,13 @@
       <c r="J180" s="3" t="n">
         <v>1.3</v>
       </c>
+      <c r="K180" s="6" t="n">
+        <v>0.789</v>
+      </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B181" s="5" t="n">
         <v>5.912705</v>
@@ -6944,10 +7489,13 @@
       <c r="J181" s="3" t="n">
         <v>1.5</v>
       </c>
+      <c r="K181" s="6" t="n">
+        <v>0.9157</v>
+      </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B182" s="5" t="n">
         <v>53.18175</v>
@@ -6976,10 +7524,13 @@
       <c r="J182" s="3" t="n">
         <v>6.9</v>
       </c>
+      <c r="K182" s="6" t="n">
+        <v>3.3469</v>
+      </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B183" s="5" t="n">
         <v>13.677243</v>
@@ -7008,10 +7559,13 @@
       <c r="J183" s="3" t="n">
         <v>2.2</v>
       </c>
+      <c r="K183" s="6" t="n">
+        <v>1.0202</v>
+      </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B184" s="5" t="n">
         <v>44.079722</v>
@@ -7040,10 +7594,13 @@
       <c r="J184" s="3" t="n">
         <v>4.7</v>
       </c>
+      <c r="K184" s="6" t="n">
+        <v>2.5032</v>
+      </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B185" s="5" t="n">
         <v>50.127511</v>
@@ -7072,10 +7629,13 @@
       <c r="J185" s="3" t="n">
         <v>6.4</v>
       </c>
+      <c r="K185" s="6" t="n">
+        <v>4.066</v>
+      </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B186" s="5" t="n">
         <v>32.514393</v>
@@ -7104,10 +7664,13 @@
       <c r="J186" s="3" t="n">
         <v>3.8</v>
       </c>
+      <c r="K186" s="6" t="n">
+        <v>2.0547</v>
+      </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B187" s="5" t="n">
         <v>24.331009</v>
@@ -7136,10 +7699,13 @@
       <c r="J187" s="3" t="n">
         <v>3.2</v>
       </c>
+      <c r="K187" s="6" t="n">
+        <v>5.1197</v>
+      </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B188" s="5" t="n">
         <v>40.334513</v>
@@ -7168,10 +7734,13 @@
       <c r="J188" s="3" t="n">
         <v>5.8</v>
       </c>
+      <c r="K188" s="6" t="n">
+        <v>2.498</v>
+      </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B189" s="5" t="n">
         <v>39.925609</v>
@@ -7200,10 +7769,13 @@
       <c r="J189" s="3" t="n">
         <v>6.8</v>
       </c>
+      <c r="K189" s="6" t="n">
+        <v>4.4859</v>
+      </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B190" s="5" t="n">
         <v>30.665404</v>
@@ -7232,10 +7804,13 @@
       <c r="J190" s="3" t="n">
         <v>4.2</v>
       </c>
+      <c r="K190" s="6" t="n">
+        <v>2.9774</v>
+      </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B191" s="5" t="n">
         <v>31.712226</v>
@@ -7264,10 +7839,13 @@
       <c r="J191" s="3" t="n">
         <v>3.5</v>
       </c>
+      <c r="K191" s="6" t="n">
+        <v>3.221</v>
+      </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B192" s="5" t="n">
         <v>31.824943</v>
@@ -7296,10 +7874,13 @@
       <c r="J192" s="3" t="n">
         <v>4.4</v>
       </c>
+      <c r="K192" s="6" t="n">
+        <v>2.3043</v>
+      </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B193" s="5" t="n">
         <v>29.467294</v>
@@ -7328,10 +7909,13 @@
       <c r="J193" s="3" t="n">
         <v>4.3</v>
       </c>
+      <c r="K193" s="6" t="n">
+        <v>1.7531</v>
+      </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B194" s="5" t="n">
         <v>49.649349</v>
@@ -7360,10 +7944,13 @@
       <c r="J194" s="3" t="n">
         <v>5.2</v>
       </c>
+      <c r="K194" s="6" t="n">
+        <v>4.5898</v>
+      </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B195" s="5" t="n">
         <v>31.599542</v>
@@ -7392,10 +7979,13 @@
       <c r="J195" s="3" t="n">
         <v>4.7</v>
       </c>
+      <c r="K195" s="6" t="n">
+        <v>3.3616</v>
+      </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B196" s="5" t="n">
         <v>40.137229</v>
@@ -7424,10 +8014,13 @@
       <c r="J196" s="3" t="n">
         <v>6.7</v>
       </c>
+      <c r="K196" s="6" t="n">
+        <v>4.3136</v>
+      </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B197" s="5" t="n">
         <v>38.268129</v>
@@ -7456,10 +8049,13 @@
       <c r="J197" s="3" t="n">
         <v>3.8</v>
       </c>
+      <c r="K197" s="6" t="n">
+        <v>1.5592</v>
+      </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B198" s="5" t="n">
         <v>19.636423</v>
@@ -7488,10 +8084,13 @@
       <c r="J198" s="3" t="n">
         <v>3.1</v>
       </c>
+      <c r="K198" s="6" t="n">
+        <v>0.8602</v>
+      </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B199" s="5" t="n">
         <v>11.334024</v>
@@ -7520,10 +8119,13 @@
       <c r="J199" s="3" t="n">
         <v>1.5</v>
       </c>
+      <c r="K199" s="6" t="n">
+        <v>0.7752</v>
+      </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B200" s="5" t="n">
         <v>18.518538</v>
@@ -7552,10 +8154,13 @@
       <c r="J200" s="3" t="n">
         <v>3.3</v>
       </c>
+      <c r="K200" s="6" t="n">
+        <v>2.5002</v>
+      </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B201" s="5" t="n">
         <v>10.942145</v>
@@ -7584,10 +8189,13 @@
       <c r="J201" s="3" t="n">
         <v>2</v>
       </c>
+      <c r="K201" s="6" t="n">
+        <v>1.1933</v>
+      </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B202" s="5" t="n">
         <v>42.53863</v>
@@ -7616,10 +8224,13 @@
       <c r="J202" s="3" t="n">
         <v>3.8</v>
       </c>
+      <c r="K202" s="6" t="n">
+        <v>3.7658</v>
+      </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B203" s="5" t="n">
         <v>33.419712</v>
@@ -7648,10 +8259,13 @@
       <c r="J203" s="3" t="n">
         <v>5.9</v>
       </c>
+      <c r="K203" s="6" t="n">
+        <v>3.0466</v>
+      </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B204" s="5" t="n">
         <v>99.069279</v>
@@ -7680,10 +8294,13 @@
       <c r="J204" s="3" t="n">
         <v>7.1</v>
       </c>
+      <c r="K204" s="6" t="n">
+        <v>4.3715</v>
+      </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B205" s="5" t="n">
         <v>33.831533</v>
@@ -7712,10 +8329,13 @@
       <c r="J205" s="3" t="n">
         <v>4.4</v>
       </c>
+      <c r="K205" s="6" t="n">
+        <v>2.6947</v>
+      </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B206" s="5" t="n">
         <v>23.564795</v>
@@ -7744,10 +8364,13 @@
       <c r="J206" s="3" t="n">
         <v>4.6</v>
       </c>
+      <c r="K206" s="6" t="n">
+        <v>1.2147</v>
+      </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B207" s="5" t="n">
         <v>37.912718</v>
@@ -7776,10 +8399,13 @@
       <c r="J207" s="3" t="n">
         <v>5.2</v>
       </c>
+      <c r="K207" s="6" t="n">
+        <v>2.7228</v>
+      </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B208" s="5" t="n">
         <v>54.414078</v>
@@ -7808,10 +8434,13 @@
       <c r="J208" s="3" t="n">
         <v>8.2</v>
       </c>
+      <c r="K208" s="6" t="n">
+        <v>2.2939</v>
+      </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B209" s="5" t="n">
         <v>34.505878</v>
@@ -7840,10 +8469,13 @@
       <c r="J209" s="3" t="n">
         <v>6.8</v>
       </c>
+      <c r="K209" s="6" t="n">
+        <v>3.4956</v>
+      </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B210" s="5" t="n">
         <v>59.645401</v>
@@ -7871,6 +8503,9 @@
       </c>
       <c r="J210" s="3" t="n">
         <v>6.1</v>
+      </c>
+      <c r="K210" s="6" t="n">
+        <v>3.7369</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10260,7 +10895,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultColWidth="11.23828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.33"/>
@@ -10271,27 +10906,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>12.5</v>
@@ -10311,7 +10946,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>15.3</v>
@@ -10331,7 +10966,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>17.6</v>
@@ -10351,7 +10986,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>28.4</v>
@@ -10371,7 +11006,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>13.5</v>
@@ -10391,7 +11026,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>23.2</v>
@@ -10411,7 +11046,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>24.9</v>
@@ -10431,7 +11066,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>15.4</v>
@@ -10451,7 +11086,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>51.4</v>
@@ -10471,7 +11106,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>10.3</v>
@@ -10491,7 +11126,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>9.2</v>
@@ -10511,7 +11146,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B13" s="10" t="n">
         <v>27.6</v>
@@ -10531,7 +11166,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>30.7</v>
@@ -10551,7 +11186,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>15.5</v>
@@ -10571,7 +11206,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>3.9</v>
@@ -10591,7 +11226,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>27.3</v>
@@ -10611,7 +11246,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>16.1</v>
@@ -10631,7 +11266,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>29.3</v>
@@ -10651,7 +11286,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>8.3</v>
@@ -10671,7 +11306,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>27.5</v>
@@ -10691,7 +11326,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>22.1</v>
@@ -10711,7 +11346,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>15</v>
@@ -10731,7 +11366,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>13.9</v>
@@ -10751,7 +11386,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>19.4</v>
@@ -10771,7 +11406,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>16.2</v>
@@ -10791,7 +11426,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>30.3</v>
@@ -10811,7 +11446,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>24.3</v>
@@ -10831,7 +11466,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>30</v>
@@ -10851,7 +11486,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>15.2</v>
@@ -10871,7 +11506,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>17</v>
@@ -10891,7 +11526,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>13.5</v>
@@ -10911,7 +11546,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>20.3</v>
@@ -10931,7 +11566,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>18.3</v>
@@ -10951,7 +11586,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>19.9</v>
@@ -10971,7 +11606,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1.8</v>
@@ -11006,22 +11641,22 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B1048576"/>
-  <sheetFormatPr defaultColWidth="11.23828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="10.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>0</v>
@@ -11029,7 +11664,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>0.33</v>
@@ -11037,7 +11672,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>0.67</v>
@@ -11045,7 +11680,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>1</v>
@@ -11069,28 +11704,28 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C37"/>
-  <sheetFormatPr defaultColWidth="11.23828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="10.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>0</v>
@@ -11098,10 +11733,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>0.33</v>
@@ -11109,10 +11744,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>1</v>
@@ -11120,10 +11755,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>1</v>
@@ -11131,10 +11766,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>0</v>
@@ -11142,10 +11777,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>0</v>
@@ -11153,10 +11788,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>0.67</v>
@@ -11164,10 +11799,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>0.33</v>
@@ -11175,10 +11810,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>0</v>
@@ -11186,10 +11821,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>0</v>
@@ -11197,10 +11832,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>0</v>
@@ -11208,10 +11843,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>0.67</v>
@@ -11219,10 +11854,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>0</v>
@@ -11230,10 +11865,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>0.33</v>
@@ -11241,10 +11876,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>0</v>
@@ -11252,10 +11887,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>0</v>
@@ -11263,10 +11898,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>0.33</v>
@@ -11274,10 +11909,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>0</v>
@@ -11285,10 +11920,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>0</v>
@@ -11296,10 +11931,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>0</v>
@@ -11307,10 +11942,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>0.33</v>
@@ -11318,10 +11953,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>0.33</v>
@@ -11329,10 +11964,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>0.67</v>
@@ -11340,10 +11975,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>0</v>
@@ -11351,10 +11986,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>0.33</v>
@@ -11362,10 +11997,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>0.67</v>
@@ -11373,10 +12008,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>1</v>
@@ -11384,10 +12019,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>0.67</v>
@@ -11395,10 +12030,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>0</v>
@@ -11406,10 +12041,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>0.33</v>
@@ -11417,10 +12052,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>0</v>
@@ -11428,10 +12063,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>0</v>
@@ -11439,10 +12074,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>0</v>
@@ -11450,10 +12085,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>1</v>
@@ -11461,10 +12096,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>0.33</v>
@@ -11472,10 +12107,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>1</v>
@@ -11498,235 +12133,235 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BU36"/>
-  <sheetFormatPr defaultColWidth="11.23828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="73" min="1" style="0" width="10.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="BU1" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="BE1" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="BF1" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="BG1" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="BI1" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="BJ1" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="BK1" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="BL1" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="BM1" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="BN1" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="BO1" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="BP1" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="BQ1" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="BR1" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="BS1" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="BT1" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="BU1" s="1" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>0</v>
@@ -11947,7 +12582,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>0.45</v>
@@ -12168,7 +12803,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>0</v>
@@ -12389,7 +13024,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>0</v>
@@ -12610,7 +13245,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>0</v>
@@ -12831,7 +13466,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>0</v>
@@ -13049,7 +13684,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>0</v>
@@ -13270,7 +13905,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>0</v>
@@ -13491,7 +14126,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>0</v>
@@ -13706,7 +14341,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>0.25</v>
@@ -13927,7 +14562,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>0</v>
@@ -14148,7 +14783,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>0</v>
@@ -14369,7 +15004,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>0</v>
@@ -14590,7 +15225,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>0</v>
@@ -14811,7 +15446,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>0</v>
@@ -15032,7 +15667,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>0</v>
@@ -15253,7 +15888,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>0</v>
@@ -15474,7 +16109,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>0</v>
@@ -15695,7 +16330,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>0</v>
@@ -15916,7 +16551,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>0</v>
@@ -16137,7 +16772,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>0</v>
@@ -16358,7 +16993,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>0</v>
@@ -16579,7 +17214,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>0</v>
@@ -16800,7 +17435,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>0</v>
@@ -17021,7 +17656,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B26" s="1" t="n">
         <v>0</v>
@@ -17242,7 +17877,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B27" s="1" t="n">
         <v>0</v>
@@ -17463,7 +18098,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B28" s="1" t="n">
         <v>0</v>
@@ -17681,7 +18316,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B29" s="1" t="n">
         <v>0</v>
@@ -17902,7 +18537,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B30" s="1" t="n">
         <v>0</v>
@@ -18123,7 +18758,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B31" s="1" t="n">
         <v>0</v>
@@ -18344,7 +18979,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B32" s="1" t="n">
         <v>0</v>
@@ -18565,7 +19200,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B33" s="1" t="n">
         <v>0</v>
@@ -18786,7 +19421,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B34" s="1" t="n">
         <v>0</v>
@@ -19007,7 +19642,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B35" s="1" t="n">
         <v>0.11</v>
@@ -19225,7 +19860,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B36" s="1" t="n">
         <v>0</v>
@@ -19461,31 +20096,31 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="11.23828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="10.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B2" s="11" t="n">
         <v>6097</v>
@@ -19502,7 +20137,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>744</v>
@@ -19519,7 +20154,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>895</v>
@@ -19536,7 +20171,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B5" s="11" t="n">
         <v>1112</v>
@@ -19553,7 +20188,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>1054</v>
@@ -19570,7 +20205,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>775</v>
@@ -19587,7 +20222,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>1288</v>
@@ -19604,7 +20239,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B9" s="11" t="n">
         <v>1680</v>
@@ -19621,7 +20256,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>53</v>
@@ -19638,7 +20273,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B11" s="11" t="n">
         <v>2808</v>
@@ -19655,7 +20290,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>282</v>
@@ -19672,7 +20307,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>120</v>
@@ -19689,7 +20324,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B14" s="11" t="n">
         <v>1586</v>
@@ -19706,7 +20341,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>736</v>
@@ -19723,7 +20358,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>193</v>
@@ -19740,7 +20375,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B17" s="11" t="n">
         <v>8139</v>
@@ -19757,7 +20392,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B18" s="11" t="n">
         <v>2985</v>
@@ -19774,7 +20409,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>892</v>
@@ -19791,7 +20426,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B20" s="11" t="n">
         <v>1980</v>
@@ -19808,7 +20443,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>530</v>
@@ -19825,7 +20460,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B22" s="11" t="n">
         <v>2092</v>
@@ -19842,7 +20477,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B23" s="11" t="n">
         <v>1397</v>
@@ -19859,7 +20494,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B24" s="11" t="n">
         <v>1472</v>
@@ -19876,7 +20511,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B25" s="11" t="n">
         <v>38910</v>
@@ -19908,25 +20543,25 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C1048576"/>
-  <sheetFormatPr defaultColWidth="11.23828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="10.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="n">
@@ -19935,7 +20570,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="n">
@@ -19944,7 +20579,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4" t="n">
@@ -19953,7 +20588,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4" t="n">
@@ -19962,10 +20597,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>50</v>
@@ -19973,7 +20608,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4" t="n">
@@ -19982,10 +20617,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.05</v>
@@ -19993,10 +20628,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>316</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>315</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>20</v>
@@ -20004,10 +20639,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>75</v>
@@ -20015,10 +20650,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.25</v>

--- a/Data point Supporting files/Germany 2020/Indicators.xlsx
+++ b/Data point Supporting files/Germany 2020/Indicators.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="322">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -989,6 +989,9 @@
   </si>
   <si>
     <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disaster coping capacity</t>
   </si>
 </sst>
 </file>
@@ -1143,7 +1146,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K1000"/>
-  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.44"/>
@@ -10895,7 +10898,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.33"/>
@@ -11641,7 +11644,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B1048576"/>
-  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="10.67"/>
   </cols>
@@ -11704,7 +11707,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C37"/>
-  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="10.67"/>
   </cols>
@@ -12133,7 +12136,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BU36"/>
-  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="73" min="1" style="0" width="10.67"/>
   </cols>
@@ -20096,7 +20099,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="10.67"/>
   </cols>
@@ -20543,7 +20546,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C1048576"/>
-  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="10.67"/>
   </cols>
@@ -20657,6 +20660,14 @@
       </c>
       <c r="C11" s="4" t="n">
         <v>0.25</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>321</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
